--- a/tests/CREATE_B_measurement_nodal/input_template.xlsx
+++ b/tests/CREATE_B_measurement_nodal/input_template.xlsx
@@ -4,7 +4,7 @@
   <fileVersion rupBuild="9303" lowestEdited="5" lastEdited="5" appName="xl"/>
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="480" yWindow="60" windowWidth="18195" windowHeight="8505" activeTab="0"/>
+    <workbookView xWindow="480" yWindow="60" windowWidth="18195" windowHeight="8505" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet r:id="rId1" sheetId="1" name="element_types"/>
